--- a/docs/03_test/部門一覧テストケース.xlsx
+++ b/docs/03_test/部門一覧テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB8B472-BFCE-46A7-91AC-0B8F52756BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB895C0-503A-42BE-A2EF-E26BD9A7241B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CE269700-E0B0-4FFB-A5F8-1DD7DC805254}"/>
   </bookViews>
@@ -72,51 +72,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>社員一覧表示単体UIテスト 須崎千穂子</t>
-    <rPh sb="0" eb="2">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>画面上部の社員一覧ボタンを押す</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウブ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>従業員一覧が表示される</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>戻るボタンを押す</t>
     <rPh sb="0" eb="1">
       <t>モド</t>
@@ -150,6 +105,51 @@
     </rPh>
     <rPh sb="8" eb="9">
       <t>ナガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門一覧表示単体UIテスト 須崎千穂子</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門上部の社員一覧ボタンを押す</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウブ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門一覧が表示される</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -238,22 +238,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>69850</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2260600</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>393267</xdr:rowOff>
+      <xdr:colOff>1896828</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1120589</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1745A511-F568-1DB4-E3B0-841A6F38EAE4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D14F143-A2B8-08B1-7D9C-E81B4AA85039}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -269,8 +269,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4743450" y="965200"/>
-          <a:ext cx="2190750" cy="317067"/>
+          <a:off x="4303059" y="694766"/>
+          <a:ext cx="1896828" cy="1120588"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -283,21 +283,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>34638</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2357011</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>1039092</xdr:rowOff>
+      <xdr:colOff>2413001</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>138982</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72E7DB6A-54EA-D466-D289-58FC8488BF9B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37800AA9-3A59-5E45-11EF-51B9652ECDF0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -313,8 +313,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4675910" y="496456"/>
-          <a:ext cx="2357010" cy="1004454"/>
+          <a:off x="4303060" y="1934882"/>
+          <a:ext cx="2413000" cy="572276"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -633,7 +633,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -641,7 +641,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -666,10 +666,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -677,15 +677,15 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/03_test/部門一覧テストケース.xlsx
+++ b/docs/03_test/部門一覧テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB895C0-503A-42BE-A2EF-E26BD9A7241B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81298A7-BE88-4D6E-911A-48DEEA930D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CE269700-E0B0-4FFB-A5F8-1DD7DC805254}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>手順</t>
     <rPh sb="0" eb="2">
@@ -72,84 +72,83 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>戻るボタンを押す</t>
-    <rPh sb="0" eb="1">
-      <t>モド</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ホームに戻る</t>
-    <rPh sb="4" eb="5">
-      <t>モド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>①正常系</t>
-    <rPh sb="1" eb="4">
-      <t>セイジョウケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>一覧表示は1つの流れしかないため、テストケースも1つである。</t>
+    <t>従業員一覧表示単体UIテスト 須崎千穂子</t>
+    <rPh sb="3" eb="5">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①ホームページの「従業員管理」から遷移する</t>
+    <rPh sb="9" eb="12">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>②画面上部のヘッダーから遷移する</t>
+    <rPh sb="1" eb="3">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウブ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面上部の従業員一覧ボタンを押す</t>
     <rPh sb="0" eb="2">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ナガ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>部門一覧表示単体UIテスト 須崎千穂子</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>部門上部の社員一覧ボタンを押す</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
+      <t>ガメン</t>
     </rPh>
     <rPh sb="2" eb="4">
       <t>ジョウブ</t>
     </rPh>
-    <rPh sb="5" eb="7">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
+    <rPh sb="8" eb="10">
       <t>イチラン</t>
     </rPh>
-    <rPh sb="13" eb="14">
+    <rPh sb="14" eb="15">
       <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部門一覧が表示される</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
+    <t>従業員一覧が表示される</t>
+    <rPh sb="0" eb="3">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
       <t>イチラン</t>
     </rPh>
-    <rPh sb="5" eb="7">
+    <rPh sb="6" eb="8">
       <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ホーム画面中の「従業員管理」ボタンを押す</t>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="8" eb="13">
+      <t>ジュウギョウインカンリ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -203,7 +202,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -213,8 +212,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -238,22 +243,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1896828</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>1120589</xdr:rowOff>
+      <xdr:colOff>1920103</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1157941</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="6" name="図 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D14F143-A2B8-08B1-7D9C-E81B4AA85039}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EED78220-B282-C471-DA2F-57660D05BCDA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -269,8 +274,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4303059" y="694766"/>
-          <a:ext cx="1896828" cy="1120588"/>
+          <a:off x="4303060" y="1419412"/>
+          <a:ext cx="1920102" cy="1157941"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -282,22 +287,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2413001</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>138982</xdr:rowOff>
+      <xdr:colOff>1920102</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>1157941</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="7" name="図 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37800AA9-3A59-5E45-11EF-51B9652ECDF0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37F13A88-32CA-48F3-B1A1-88F13BABDB2D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -306,15 +311,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4303060" y="1934882"/>
-          <a:ext cx="2413000" cy="572276"/>
+          <a:off x="4303059" y="2853765"/>
+          <a:ext cx="1920102" cy="1157941"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -623,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{619CB1A3-9864-4F09-832B-BDB48215BE19}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="21.5" style="1" customWidth="1"/>
@@ -632,66 +637,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" ht="20.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="94.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="3" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="98.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="97.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
-        <v>7</v>
+      <c r="C9" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A8:D8"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/03_test/部門一覧テストケース.xlsx
+++ b/docs/03_test/部門一覧テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81298A7-BE88-4D6E-911A-48DEEA930D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12ECF804-D296-4AB1-B061-6846BAD068F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CE269700-E0B0-4FFB-A5F8-1DD7DC805254}"/>
   </bookViews>
@@ -72,29 +72,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>従業員一覧表示単体UIテスト 須崎千穂子</t>
-    <rPh sb="3" eb="5">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>①ホームページの「従業員管理」から遷移する</t>
-    <rPh sb="9" eb="12">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>②画面上部のヘッダーから遷移する</t>
     <rPh sb="1" eb="3">
       <t>ガメン</t>
@@ -108,46 +85,60 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>画面上部の従業員一覧ボタンを押す</t>
+    <t>部署一覧表示単体UIテスト 須崎千穂子</t>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①ホームページの「部署管理」から遷移する</t>
+    <rPh sb="11" eb="13">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面上部の部署一覧ボタンを押す</t>
     <rPh sb="0" eb="2">
       <t>ガメン</t>
     </rPh>
     <rPh sb="2" eb="4">
       <t>ジョウブ</t>
     </rPh>
-    <rPh sb="8" eb="10">
+    <rPh sb="7" eb="9">
       <t>イチラン</t>
     </rPh>
-    <rPh sb="14" eb="15">
+    <rPh sb="13" eb="14">
       <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>従業員一覧が表示される</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
+    <t>部署一覧が表示される</t>
+    <rPh sb="2" eb="4">
       <t>イチラン</t>
     </rPh>
-    <rPh sb="6" eb="8">
+    <rPh sb="5" eb="7">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ホーム画面中の「従業員管理」ボタンを押す</t>
+    <t>ホーム画面中の「部署管理」ボタンを押す</t>
     <rPh sb="3" eb="5">
       <t>ガメン</t>
     </rPh>
     <rPh sb="5" eb="6">
       <t>ナカ</t>
     </rPh>
-    <rPh sb="8" eb="13">
-      <t>ジュウギョウインカンリ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
+    <rPh sb="17" eb="18">
       <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -213,13 +204,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -249,16 +240,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1920103</xdr:colOff>
+      <xdr:colOff>2388153</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>1157941</xdr:rowOff>
+      <xdr:rowOff>742980</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EED78220-B282-C471-DA2F-57660D05BCDA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C75FA80E-74A4-B98D-8350-2BDAB5B5A9C9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -274,8 +265,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4303060" y="1419412"/>
-          <a:ext cx="1920102" cy="1157941"/>
+          <a:off x="4306958" y="1435652"/>
+          <a:ext cx="2388152" cy="742980"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -293,16 +284,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1920102</xdr:colOff>
+      <xdr:colOff>2388152</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>1157941</xdr:rowOff>
+      <xdr:rowOff>742980</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37F13A88-32CA-48F3-B1A1-88F13BABDB2D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{545F587A-C7A1-45C1-B470-6BDFBC751914}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -318,8 +309,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4303059" y="2853765"/>
-          <a:ext cx="1920102" cy="1157941"/>
+          <a:off x="4306957" y="2871304"/>
+          <a:ext cx="2388152" cy="742980"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -637,24 +628,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="A1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="5" t="s">
-        <v>5</v>
+      <c r="A2" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="5" t="s">
-        <v>6</v>
+      <c r="A3" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -667,12 +658,12 @@
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="A5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
@@ -700,12 +691,12 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
+      <c r="A8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
     </row>
     <row r="9" spans="1:4" ht="98.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
